--- a/Mechanical/Buying List.xlsx
+++ b/Mechanical/Buying List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5486BE3-16EC-468E-AC9E-C017A32C43EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA8ECE-2CDE-4F2F-A6CD-342296FC77AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
   <si>
     <t>Component</t>
   </si>
@@ -86,9 +86,6 @@
     <t>(Take more for more motors)</t>
   </si>
   <si>
-    <t>6x6mm Solid Pins 50 Units</t>
-  </si>
-  <si>
     <t>https://es.aliexpress.com/item/1005009576693979.html?spm=a2g0o.productlist.main.6.1a877b3c2Fn66T&amp;algo_pvid=783ef9cf-4d19-4659-b80d-1c10f7e1e8c5&amp;algo_exp_id=783ef9cf-4d19-4659-b80d-1c10f7e1e8c5-5&amp;pdp_ext_f=%7B%22order%22%3A%2225%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%212.12%211.80%21%21%2117.06%2114.50%21%402101ea8c17620079193144001e08bb%2112000049516358233%21sea%21ES%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A89c66183%3Bm03_new_user%3A-29895&amp;curPageLogUid=N1LNBeR6Cvw2&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009576693979%7C_p_origin_prod%3A</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
     <t>LCSC</t>
   </si>
   <si>
-    <t>PCBWay</t>
-  </si>
-  <si>
     <t>AliExpress</t>
   </si>
   <si>
@@ -158,9 +152,6 @@
     <t>Invention</t>
   </si>
   <si>
-    <t>BHSBHCS ASME B18.3.4M - M3 x 0.5 x 45 Steel Grade 2 Plain</t>
-  </si>
-  <si>
     <t>Hexagon = Cylindrical head + allen socket</t>
   </si>
   <si>
@@ -168,6 +159,18 @@
   </si>
   <si>
     <t>Printed Cycloidal PLA</t>
+  </si>
+  <si>
+    <t>Hexagon Socket Head Cap Screw ISO 4762 - M2 x 8 Steel 4.6 Plain</t>
+  </si>
+  <si>
+    <t>Hexagon Socket Head- M3 x 0.5 x 45 Steel Grade 2 Plain (48 mm rosca)</t>
+  </si>
+  <si>
+    <t>6x12mm Solid Pins 30 Units</t>
+  </si>
+  <si>
+    <t>JLCPCB</t>
   </si>
 </sst>
 </file>
@@ -1129,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>8</v>
@@ -1159,10 +1162,10 @@
         <v>7</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H2" s="10">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1189,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1219,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H4" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1234,40 +1237,40 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="13">
+        <v>3.71</v>
+      </c>
+      <c r="D5" s="11">
+        <v>3</v>
+      </c>
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="14">
+        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
+        <v>12.129999999999999</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="13">
-        <v>2.74</v>
-      </c>
-      <c r="D5" s="11">
-        <v>2</v>
-      </c>
-      <c r="E5" s="13">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" s="14">
-        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>7.7000000000000011</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="11">
@@ -1275,10 +1278,10 @@
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1288,34 +1291,36 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="13"/>
+        <v>44</v>
+      </c>
+      <c r="C7" s="13">
+        <v>13.23</v>
+      </c>
       <c r="D7" s="11">
         <v>1</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H7" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>0</v>
+        <v>13.23</v>
       </c>
       <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="13">
         <v>2.68</v>
@@ -1327,25 +1332,25 @@
         <v>0</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H8" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>5.36</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="13">
         <v>2.11</v>
@@ -1357,22 +1362,22 @@
         <v>0</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
         <v>4.22</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>14</v>
@@ -1383,10 +1388,10 @@
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1396,10 +1401,10 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="13">
         <v>0</v>
@@ -1411,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H11" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1424,10 +1429,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" s="13">
         <v>0</v>
@@ -1439,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H12" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1452,10 +1457,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" s="13">
         <v>0</v>
@@ -1467,10 +1472,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H13" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1480,10 +1485,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="13">
         <v>0</v>
@@ -1495,10 +1500,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="G14" s="25">
+        <v>8</v>
       </c>
       <c r="H14" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1508,10 +1513,10 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="13">
         <v>0</v>
@@ -1523,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="G15" s="25">
+        <v>4</v>
       </c>
       <c r="H15" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1536,10 +1541,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="13">
         <v>0</v>
@@ -1551,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1564,10 +1569,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="13">
         <v>0</v>
@@ -1579,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="G17" s="25">
+        <v>16</v>
       </c>
       <c r="H17" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1592,10 +1597,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="13">
         <v>0</v>
@@ -1607,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>28</v>
+        <v>26</v>
+      </c>
+      <c r="G18" s="25">
+        <v>11</v>
       </c>
       <c r="H18" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1634,7 +1639,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="13"/>
@@ -1650,7 +1655,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="13"/>
@@ -1688,7 +1693,7 @@
       <c r="G23" s="25"/>
       <c r="H23" s="14">
         <f>SUM(Table1[Total])</f>
-        <v>62.230000000000004</v>
+        <v>79.89</v>
       </c>
       <c r="I23" s="11"/>
     </row>

--- a/Mechanical/Buying List.xlsx
+++ b/Mechanical/Buying List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC BLDC\Mechanical\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AA8ECE-2CDE-4F2F-A6CD-342296FC77AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1954E93-5775-4E77-A08B-D4BD2189A806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
   <si>
     <t>Component</t>
   </si>
@@ -398,6 +398,20 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -427,6 +441,29 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -472,175 +509,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -669,84 +537,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -755,6 +545,216 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -822,18 +822,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:I23" totalsRowCount="1" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
   <autoFilter ref="A1:I22" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="18" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="17" totalsRowDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="16" totalsRowDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity" dataDxfId="15" totalsRowDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="14" totalsRowDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="13" totalsRowDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="12" totalsRowDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="1">
+    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Total])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="10" totalsRowDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1255,7 +1255,7 @@
         <v>25</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1272,20 +1272,22 @@
       <c r="B6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="13"/>
+      <c r="C6" s="13">
+        <v>61.53</v>
+      </c>
       <c r="D6" s="11">
         <v>1</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="25" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>0</v>
+        <v>61.53</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -1364,8 +1366,8 @@
       <c r="F9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>26</v>
+      <c r="G9" s="25">
+        <v>1</v>
       </c>
       <c r="H9" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1391,7 +1393,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1693,13 +1695,13 @@
       <c r="G23" s="25"/>
       <c r="H23" s="14">
         <f>SUM(Table1[Total])</f>
-        <v>79.89</v>
+        <v>141.42000000000002</v>
       </c>
       <c r="I23" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:G23">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Mechanical/Buying List.xlsx
+++ b/Mechanical/Buying List.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1954E93-5775-4E77-A08B-D4BD2189A806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF5D17A-30EF-4F7D-8806-47D19973AA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
   <si>
     <t>Component</t>
   </si>
@@ -398,20 +398,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -441,29 +427,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -509,6 +472,175 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF92D050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -537,6 +669,84 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <vertical/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -545,216 +755,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <vertical/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF92D050"/>
-      </font>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -822,18 +822,18 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}" name="Table1" displayName="Table1" ref="A1:I23" totalsRowCount="1" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19">
   <autoFilter ref="A1:I22" xr:uid="{57113999-89B8-4DCA-AAEB-0496B38A0B13}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="1" xr3:uid="{C01A5BB4-2776-4DA4-B397-20536FB6B151}" name="Component" dataDxfId="18" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{D16A6BB5-FB54-4A08-8F36-6F894F571CA2}" name="Supplier" dataDxfId="17" totalsRowDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{13E6D449-D029-4B98-A474-567EF4C137DD}" name="Unit Price" dataDxfId="16" totalsRowDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{BFC6BC80-26FB-482F-B354-EBAC0B59B079}" name="Quantity" dataDxfId="15" totalsRowDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{E17DAC7E-1E39-4AF4-8109-E85C3BEA4D94}" name="Shipping Costs" dataDxfId="14" totalsRowDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{80648434-14FA-49B4-BA1C-C16B6DFD9A61}" name="Purchased" dataDxfId="13" totalsRowDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{2A4D153E-2215-40C4-B217-8FADF5785568}" name="Arrived" dataDxfId="12" totalsRowDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{9BE18441-967B-45FF-8A88-16AF220F7381}" name="Total" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(Table1[Total])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{B8F06C12-DD71-45A3-886F-8113BE8A9BDA}" name="Link" dataDxfId="10" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1286,8 +1286,7 @@
         <v>26</v>
       </c>
       <c r="H6" s="14">
-        <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
-        <v>61.53</v>
+        <v>64.11</v>
       </c>
       <c r="I6" s="11"/>
     </row>
@@ -1586,10 +1585,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="25">
-        <v>16</v>
+        <v>25</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="H17" s="26">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1695,13 +1694,13 @@
       <c r="G23" s="25"/>
       <c r="H23" s="14">
         <f>SUM(Table1[Total])</f>
-        <v>141.42000000000002</v>
+        <v>144</v>
       </c>
       <c r="I23" s="11"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:G23">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Mechanical/Buying List.xlsx
+++ b/Mechanical/Buying List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angel\Desktop\Proyectos\FOC_BLDC\Mechanical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF5D17A-30EF-4F7D-8806-47D19973AA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729BE44D-F2ED-4F66-AFE8-7EE9039F2437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Components" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="45">
   <si>
     <t>Component</t>
   </si>
@@ -1192,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1283,7 +1283,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="14">
         <v>64.11</v>
@@ -1308,7 +1308,7 @@
         <v>25</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1336,7 +1336,7 @@
         <v>25</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
@@ -1365,8 +1365,8 @@
       <c r="F9" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="25">
-        <v>1</v>
+      <c r="G9" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="H9" s="14">
         <f>Table1[[#This Row],[Unit Price]]*Table1[[#This Row],[Quantity]]+Table1[[#This Row],[Shipping Costs]]</f>
